--- a/src/attributions/attributions_ig_traj_491.xlsx
+++ b/src/attributions/attributions_ig_traj_491.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2307795771518228</v>
+        <v>0.2221595528590395</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03893714392238969</v>
+        <v>-0.07739315557762264</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0790570297153937</v>
+        <v>-0.06651955792141631</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1029,16 +1029,16 @@
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.165509366073027</v>
+        <v>0.2586175937347898</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03086878090515586</v>
+        <v>-0.07286559153601732</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.08694281717343948</v>
+        <v>-0.09783645036257789</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1053,28 +1053,28 @@
         <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09944803416898601</v>
+        <v>0.06844820336282094</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02449588496801963</v>
+        <v>0.005156589092060594</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03118235792978538</v>
+        <v>-0.01086923651897878</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1083,49 +1083,49 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.001373937841648899</v>
+        <v>0.09993978529846732</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.06041458203621989</v>
+        <v>-0.08739904052855293</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02999363267516154</v>
+        <v>0.04361923071635135</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04523580934702712</v>
+        <v>0.09596579567648557</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.06713089000414145</v>
+        <v>-0.03020738750253838</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06858876405575698</v>
+        <v>0.1156923048307911</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
@@ -1134,22 +1134,22 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3915615056499445</v>
+        <v>0.3692011715995634</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.05243633228513025</v>
+        <v>-0.2529490074457438</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1199543066279421</v>
+        <v>-0.07229755724201528</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0</v>
@@ -1158,49 +1158,49 @@
         <v>-0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.0688068786726474</v>
+        <v>-0.06269910626099211</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.03047485744213313</v>
+        <v>-0.01304577189486992</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.2230187319886479</v>
+        <v>-0.05648171807010348</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.04698117451755306</v>
+        <v>-0.04694140006882575</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.09881584916474256</v>
+        <v>0.03888367027198729</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0785646656477204</v>
+        <v>0.1019361773363206</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
@@ -1218,19 +1218,19 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2443680147104513</v>
+        <v>0.211007946985119</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0382519825349532</v>
+        <v>-0.1433302294204528</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.006356020741280445</v>
+        <v>-0.02174263191402381</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
@@ -1245,46 +1245,46 @@
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.09940801769972421</v>
+        <v>-0.1556286639740482</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0309673116971904</v>
+        <v>0.1022796367886354</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.03251164910554723</v>
+        <v>0.02466031695003211</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01253231654785338</v>
+        <v>-0.0471446748331058</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.04594697679619025</v>
+        <v>0.03974806987101652</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.08856300405769392</v>
+        <v>-0.01265322255317978</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,76 +1293,76 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1030111916341365</v>
+        <v>-0.175096360250419</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.05435554961865166</v>
+        <v>0.1118003894950809</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.03336670403422284</v>
+        <v>0.04540071157442339</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.05355684920843454</v>
+        <v>-0.1161470982853747</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.07151423822548236</v>
+        <v>0.06668231145604175</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.02130197713861474</v>
+        <v>-0.03221333732885991</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.05297435025804704</v>
+        <v>-0.1079387123543384</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.04034260683730621</v>
+        <v>0.08778954285782639</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.02785838461821313</v>
+        <v>-0.09683000215687414</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
@@ -1380,79 +1380,79 @@
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05643169248330348</v>
+        <v>-0.0945146505827278</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.09269851500585051</v>
+        <v>0.003880127389259737</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.01484660834966138</v>
+        <v>0.004615949105964404</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1363698997164579</v>
+        <v>-0.08827529480081751</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0314657466513526</v>
+        <v>0.08401563548576073</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0375704791103169</v>
+        <v>0.0515626815630772</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.007461119507492368</v>
+        <v>0.05224206782257867</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.02716828402535566</v>
+        <v>0.04876361792462119</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03854603282399718</v>
+        <v>-0.02674986653865754</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,46 +1461,46 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.09594713657040368</v>
+        <v>-0.1893643935122018</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.04012953690312781</v>
+        <v>0.1220339248061577</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.04097736891614029</v>
+        <v>0.01879288167077928</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01321833745008183</v>
+        <v>-0.08831814217358498</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.002111678607017571</v>
+        <v>-0.05968211758559255</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.03430385608569621</v>
+        <v>0.02483694265455548</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1509,49 +1509,49 @@
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01619028532651895</v>
+        <v>-0.1471576076754146</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1189893939917338</v>
+        <v>0.3179026330785242</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.02506275920440572</v>
+        <v>0.1171403142585072</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01359656455615181</v>
+        <v>-0.1211547474934206</v>
       </c>
       <c r="GA2" t="n">
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.006028169501381263</v>
+        <v>0.04226326460558823</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1568,100 +1568,100 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03719548718424318</v>
+        <v>-0.1542320996576436</v>
       </c>
       <c r="B3" t="n">
-        <v>0.256618138114229</v>
+        <v>0.3272170147230991</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04303188103523301</v>
+        <v>-0.1297945554831968</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1342394752427075</v>
+        <v>-0.3183686235573169</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002500760250682973</v>
+        <v>-0.1216185904181005</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1080660719282006</v>
+        <v>0.4210566410219887</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06096884873333965</v>
+        <v>-0.2288797971688989</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1136084108705026</v>
+        <v>-0.2746980264707944</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03722704517840898</v>
+        <v>-0.01142655680837582</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01098722573198602</v>
+        <v>0.09516601037574363</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.06622413331428868</v>
+        <v>-0.2679165255660685</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.04697038673769882</v>
+        <v>-0.3015639185710386</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03423294441845252</v>
+        <v>0.07127133635742165</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1775860095708144</v>
+        <v>0.1156061362571427</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1227818140655747</v>
+        <v>0.1079207468202544</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1670,16 +1670,16 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1598779287196938</v>
+        <v>0.2610942829611899</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.005077501464999611</v>
+        <v>-0.08833405732463122</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01407821865297684</v>
+        <v>0.1878576044946256</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.03428356275448115</v>
+        <v>0.07190480376601145</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1700,49 +1700,49 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.06737130877644433</v>
+        <v>-0.1224586423279779</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.08934597208931021</v>
+        <v>-0.07244077442240386</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.315818123256425</v>
+        <v>0.5855976379363632</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3218943498501637</v>
+        <v>-0.09647343011676598</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.1826301035545321</v>
+        <v>-0.3047102074462946</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.04262846709665378</v>
+        <v>-0.003875582194591521</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.06719806846061531</v>
+        <v>-0.06665181975609523</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.1704947739084517</v>
+        <v>0.07324919346190971</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1751,109 +1751,109 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.07483311341001365</v>
+        <v>-0.3550076588353511</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.007948375537540769</v>
+        <v>0.07063953314185674</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.03353318504870522</v>
+        <v>0.09561420771123555</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2125680513318001</v>
+        <v>0.2655842441070516</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.08083170860251938</v>
+        <v>0.267213326621472</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.02639609466969007</v>
+        <v>-0.05532556546150746</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1713618361097054</v>
+        <v>0.3728030313227858</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.06400196626112649</v>
+        <v>-0.3686736630860491</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.08432780349444888</v>
+        <v>-0.5590664215278746</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.024497634786882</v>
+        <v>0.07609994968522264</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1048340364332778</v>
+        <v>-0.228560827912492</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.02493152777595641</v>
+        <v>0.07095902393165043</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.09888491252000325</v>
+        <v>0.2352097436128946</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.02253383370489659</v>
+        <v>-0.04151965172553544</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01310025397324319</v>
+        <v>-0.1377609960795846</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.05126990691560068</v>
+        <v>-0.08418479448826803</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
@@ -1862,49 +1862,49 @@
         <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0.02125141845091224</v>
+        <v>0.09733335942151861</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.01843381089789205</v>
+        <v>0.04743958895174068</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.1263828714218179</v>
+        <v>-0.2305676530595586</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.03513844301329987</v>
+        <v>-0.002720186553885197</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.06594574662818373</v>
+        <v>0.271150193574328</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08124476109220988</v>
+        <v>0.03826893849592725</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.4673530829331953</v>
+        <v>-0.4274893839972263</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1625381504552946</v>
+        <v>-0.2216132755985613</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
@@ -1913,70 +1913,70 @@
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.04986165534351507</v>
+        <v>0.08640285200330043</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.00438880770113148</v>
+        <v>-0.04374710817981133</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.1074460636015915</v>
+        <v>-0.1361213267894722</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.006189952439991288</v>
+        <v>0.02335593673907318</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.04229814346375561</v>
+        <v>-0.04035540814280324</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0330241620077119</v>
+        <v>-0.04535584812065955</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.1357139580626478</v>
+        <v>-0.1978984851082634</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.004745984985528289</v>
+        <v>-0.2661513939820733</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.06538079161508446</v>
+        <v>-0.1886864437220652</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.01945804909035395</v>
+        <v>0.1341364266637592</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0399061306693724</v>
+        <v>-0.1163302241819327</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,118 +1985,118 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.03138987757804712</v>
+        <v>0.05274438792183232</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.1187049277437411</v>
+        <v>0.1966672087842676</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.04184490476874161</v>
+        <v>0.01746553502679213</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1085693127680043</v>
+        <v>-0.03573346738507049</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1166685244899314</v>
+        <v>-0.1832053274694307</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.01247644247527697</v>
+        <v>0.1241232734910637</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.02025717017285107</v>
+        <v>0.07494222979403663</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.1321889772790297</v>
+        <v>-0.2881160399680897</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.05994751300308227</v>
+        <v>0.07059077271045003</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.02432746457391994</v>
+        <v>0.2852019669881298</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0.05114582507016178</v>
+        <v>0.06582604126165909</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.06374890986024977</v>
+        <v>-0.2491278423952318</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.06960990716933484</v>
+        <v>-0.006981090934326006</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.03641544054919556</v>
+        <v>0.2568734721417947</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1131627059782436</v>
+        <v>0.1834409336020836</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.03994851629218664</v>
+        <v>-0.1975980131531492</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.09722116268398573</v>
+        <v>0.6234088541391853</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
@@ -2105,34 +2105,34 @@
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0.002949043049378914</v>
+        <v>0.0497842272295837</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.00450972188790238</v>
+        <v>0.182331866381783</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.147123101428963</v>
+        <v>-0.191322529349156</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1275938979535992</v>
+        <v>0.4319728892211279</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3207047689043198</v>
+        <v>0.337299635116391</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,25 +2149,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05695260834035291</v>
+        <v>0.01091630067186084</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2334088116172841</v>
+        <v>-0.2091112853087936</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2535410093269443</v>
+        <v>0.3375246476084911</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,13 +2176,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03794430506787212</v>
+        <v>-0.05225029892160026</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2106922256821722</v>
+        <v>-0.1536569795510001</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
@@ -2191,25 +2191,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03401197123786172</v>
+        <v>0.09147913807168659</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0291873136103318</v>
+        <v>-0.03510509395142092</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.03989610107597789</v>
+        <v>-0.02941396548896023</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
@@ -2218,52 +2218,52 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04855153806240411</v>
+        <v>-0.0112600018305506</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0532343884415455</v>
+        <v>-0.04316210818171003</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.01916567666853537</v>
+        <v>-0.03986668226617344</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1092324835994158</v>
+        <v>0.1161562044746438</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.05838664747937292</v>
+        <v>0.1020279138781144</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.135102156883607</v>
+        <v>-0.07471400437837483</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4252372622674989</v>
+        <v>0.5238326714192632</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,13 +2284,13 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.02895056407033319</v>
+        <v>0.0003414856437390021</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.1592024353740707</v>
+        <v>-0.1210532854896702</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>-0</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1714042579743998</v>
+        <v>0.02841961633013601</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.0935795822586353</v>
+        <v>-0.03528354433728248</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.1426789201118063</v>
+        <v>-0.1652370800203957</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
@@ -2329,34 +2329,34 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05257613470647306</v>
+        <v>-0.02150234434068146</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.04421269409588068</v>
+        <v>0.08915921414284564</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0265045761901997</v>
+        <v>0.02490188964251641</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1957616163758044</v>
+        <v>0.2868540528477204</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01490032092946012</v>
+        <v>-0.004425324073544305</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.1276045673088956</v>
+        <v>-0.1807257415796581</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
@@ -2380,25 +2380,25 @@
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1107549642760581</v>
+        <v>-0.2058885726589356</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.001237338553367463</v>
+        <v>-0.02060916274416018</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.07637107422821707</v>
+        <v>0.1046382442936631</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.03058837092295687</v>
+        <v>-0.05509478275316681</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,232 +2419,232 @@
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002693403843497691</v>
+        <v>-0.0133886078910212</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.02916297288239184</v>
+        <v>0.04870127022550825</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.09123631773166443</v>
+        <v>-0.1993154612989358</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01231108474140291</v>
+        <v>-0.01445173573459888</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.1010435431513922</v>
+        <v>0.1207243514825966</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.07466079988365953</v>
+        <v>-0.1185337732796494</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09233567837374278</v>
+        <v>-0.1173274921344402</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.008709839096565735</v>
+        <v>0.06678200319978651</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06507223918770709</v>
+        <v>-0.06477464879915894</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.09308263416254632</v>
+        <v>-0.0597717721885788</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.07089354428946885</v>
+        <v>-0.05920151954953551</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.07337563347644199</v>
+        <v>-0.09569587335921118</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.03699129181633923</v>
+        <v>-0.1244604073949256</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0003308675402548039</v>
+        <v>0.05984266313316026</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.108058719528355</v>
+        <v>-0.1259690395358289</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
         <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.08646183866807025</v>
+        <v>-0.04778937435460863</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.09202418295650659</v>
+        <v>0.06210218193400119</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.03223665269645034</v>
+        <v>0.06295499454289448</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.06116527673499484</v>
+        <v>0.03906877831022962</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.03186224177811216</v>
+        <v>0.08985453604470436</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.08082392547763242</v>
+        <v>-0.2212191809693447</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.006254607219130643</v>
+        <v>-0.06033080431140157</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.07974760680880731</v>
+        <v>0.1041505969859157</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.008586129160002495</v>
+        <v>-0.1973918317370973</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.003399749721923287</v>
+        <v>0.09919298027396672</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.099371761333263</v>
+        <v>0.1152169199467029</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.1912417133323097</v>
+        <v>-0.2572103057689267</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,37 +2662,37 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.02960361888252839</v>
+        <v>-0.02253581305350617</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.06542326809466885</v>
+        <v>0.03992803225075575</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.04559603385863618</v>
+        <v>-0.09052749979090098</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.05995302493201932</v>
+        <v>0.06957451860019946</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2218831389103913</v>
+        <v>0.2819542075889072</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06525454787307136</v>
+        <v>-0.09963301932551943</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02446085880476079</v>
+        <v>-0.07717291498865081</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2736,130 +2736,130 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1572592291468853</v>
+        <v>0.2827178218271955</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1074615216054634</v>
+        <v>-0.1889954854795051</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02966212295780611</v>
+        <v>-0.1031403730982577</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09494658150128446</v>
+        <v>0.1012268519280813</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002280543510814958</v>
+        <v>-0.02720665245899883</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07524169789373567</v>
+        <v>-0.05410790119182374</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04768600393813992</v>
+        <v>0.03124754807119901</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01127444710502883</v>
+        <v>-0.1968428428218832</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.008791321568099426</v>
+        <v>0.09817086073311916</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01074537754199097</v>
+        <v>0.1298211526808701</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05256190356804132</v>
+        <v>-0.1318050605544053</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.06043121650708733</v>
+        <v>0.1169286873974068</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3423958299325714</v>
+        <v>0.477063635638006</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01179909749845729</v>
+        <v>-0.1930053012639414</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.145334578716768</v>
+        <v>-0.2192263058281388</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
@@ -2871,22 +2871,22 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02489710923693309</v>
+        <v>-0.09908157566541215</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.0426452536703753</v>
+        <v>-0.03388481845685311</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1170256314440643</v>
+        <v>-0.06413773323891121</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2898,16 +2898,16 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0656484818241805</v>
+        <v>-0.002406292479396108</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.06225807700640124</v>
+        <v>0.03192499494565589</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1219653817345663</v>
+        <v>0.1345714995581415</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2925,19 +2925,19 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1613519063632852</v>
+        <v>0.2933393225910483</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.006430511929518299</v>
+        <v>-0.09495842313659035</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.09197139761945861</v>
+        <v>-0.05976480063158617</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2946,157 +2946,157 @@
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.07657539168474629</v>
+        <v>-0.1614399113064301</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02456204100357693</v>
+        <v>0.1506500999905307</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.03101648252335065</v>
+        <v>0.03052980370806233</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01671859851027752</v>
+        <v>-0.04302937182382092</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.03032833931584742</v>
+        <v>0.07667566825947936</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.05449598879232894</v>
+        <v>0.007955222103822443</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.07004423096279098</v>
+        <v>-0.1548717743306849</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03563646035862902</v>
+        <v>0.1462829848148112</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.02472835197253782</v>
+        <v>0.03552419976041291</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.03662713308305435</v>
+        <v>-0.08594458971899023</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0609873149355175</v>
+        <v>0.07738787210084296</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.0212884327326897</v>
+        <v>-0.05956922960908932</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.02955719377108113</v>
+        <v>-0.08562327793966287</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.07816758215792267</v>
+        <v>0.07678223618306558</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.009639987226219743</v>
+        <v>-0.0464204217519209</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.04590316171323203</v>
+        <v>-0.04985664095539252</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.05628604004719846</v>
+        <v>-0.1390182519852632</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02454258372674894</v>
+        <v>-0.03300306500897077</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
@@ -3114,52 +3114,52 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1132222203796588</v>
+        <v>-0.1379290516187551</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.06905079172661625</v>
+        <v>0.1335365402013954</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04419898417798781</v>
+        <v>0.05127563075174595</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.04767318204429551</v>
+        <v>0.05570136641248857</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02007307828102033</v>
+        <v>0.07219335427299994</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.03623052414374323</v>
+        <v>-0.04161986878162507</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
@@ -3168,106 +3168,106 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.07057874456401313</v>
+        <v>-0.176848039641253</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03652465287210874</v>
+        <v>0.1598755771865872</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02090273277099505</v>
+        <v>0.008864963126353499</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.021840949191103</v>
+        <v>-0.0803753388591337</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02554181217271488</v>
+        <v>-0.003334940974759316</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.04394882130843097</v>
+        <v>-0.01072739618354918</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
         <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.01745788392746508</v>
+        <v>-0.1754712346912906</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1145429304146209</v>
+        <v>0.2513023347832603</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.07289688862878832</v>
+        <v>0.1414436942676346</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.02224496018915954</v>
+        <v>-0.1673945611445001</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.03434642093029764</v>
+        <v>0.1046818597471923</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.1202742505190525</v>
+        <v>-0.152632923815286</v>
       </c>
       <c r="C6" t="n">
         <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.005260586745158256</v>
+        <v>-0.004549061568468761</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01431247575646105</v>
+        <v>0.04474541661410099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3780221090799563</v>
+        <v>0.148777259703817</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -3302,28 +3302,28 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08967576334530256</v>
+        <v>-0.198596933214611</v>
       </c>
       <c r="L6" t="n">
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00187553594742461</v>
+        <v>0.004304173100196936</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0422742733357882</v>
+        <v>0.1172605665652443</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2817084495804351</v>
+        <v>0.1200055059050196</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,46 +3332,46 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07144907152135127</v>
+        <v>-0.08511057138613493</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07332547370094804</v>
+        <v>0.0490744441167676</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1218470052046158</v>
+        <v>-0.06045844235293686</v>
       </c>
       <c r="X6" t="n">
-        <v>0.110001343811795</v>
+        <v>0.07493081220534052</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.004433043149069055</v>
+        <v>0.01444083672751426</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.005071248234526194</v>
+        <v>0.05753432645353747</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0884627621294214</v>
+        <v>0.0393588844190331</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.02727939651981597</v>
+        <v>-0.03891071331319033</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -3383,82 +3383,82 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.04521804404800329</v>
+        <v>-0.08796869828493283</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.02858958893291007</v>
+        <v>-0.05428609264644288</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.09385906013417074</v>
+        <v>-0.14190609181511</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.123442771377375</v>
+        <v>0.05682021248111739</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.06359310266224887</v>
+        <v>-0.3562264771553815</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.03048910092752808</v>
+        <v>-0.02876901795434441</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1125769929632053</v>
+        <v>-0.1059140871942281</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.391496490158118</v>
+        <v>0.2915072701069085</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.2003740721785073</v>
+        <v>0.1886525079056839</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.08842521683361811</v>
+        <v>0.05722663561120574</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03285235936760575</v>
+        <v>0.1318973781705399</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1563833910668242</v>
+        <v>0.00237427599873463</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,46 +3467,46 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1370592211440086</v>
+        <v>-0.01667459645703808</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.08418543685556251</v>
+        <v>-0.06711147471989833</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.02434166697971262</v>
+        <v>-0.1015936400927109</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.02457966432050576</v>
+        <v>0.01356168799515159</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.01572371649314238</v>
+        <v>-0.2154713252576022</v>
       </c>
       <c r="BW6" t="n">
         <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.08236908204012752</v>
+        <v>-0.0410544593816991</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.08933817709967172</v>
+        <v>-0.06707700617301114</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1540080749567542</v>
+        <v>0.1952007443850205</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
@@ -3518,28 +3518,28 @@
         <v>-0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.05365322233530457</v>
+        <v>0.1644641545691108</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01462748426398402</v>
+        <v>-0.01023612905971576</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.01848526279772897</v>
+        <v>-0.02120143778886701</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.1189966658491855</v>
+        <v>-0.07616282934181207</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
@@ -3548,52 +3548,52 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.001008656759996532</v>
+        <v>0.05040386448524284</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.004596580246232615</v>
+        <v>0.005278251870149813</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0409264541722173</v>
+        <v>-0.003775799712867478</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01894511739289268</v>
+        <v>-0.06120976365680118</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU6" t="n">
         <v>0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02265884084216054</v>
+        <v>0.1763767057774493</v>
       </c>
       <c r="CX6" t="n">
         <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01319233792879373</v>
+        <v>-0.02143188629009571</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0219834531144458</v>
+        <v>-0.05238705058565903</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.132375077794544</v>
+        <v>-0.08429525250473947</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>-0</v>
@@ -3602,52 +3602,52 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.09778039138955752</v>
+        <v>0.002332158492065062</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.1545444500555137</v>
+        <v>-0.04475866807352002</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.1318138802051031</v>
+        <v>0.08224650361988103</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.02663336990386928</v>
+        <v>-0.0686385764441938</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.05185580106056043</v>
+        <v>0.1377743611055097</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.07779822376961297</v>
+        <v>0.03474381318110718</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03830129161893304</v>
+        <v>0.01163685278822284</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.02623180014235922</v>
+        <v>-0.05028536527536439</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,46 +3656,46 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.01812741092320917</v>
+        <v>0.1234118941436767</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.03680138034709374</v>
+        <v>0.1440092662405545</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0044660706061402</v>
+        <v>-0.005184828946687139</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.08645941716586165</v>
+        <v>0.1720412409755377</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0107067856516978</v>
+        <v>0.1298348507943052</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.07145964797956697</v>
+        <v>-0.05624666087206619</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.01691379264975056</v>
+        <v>-0.04697396118056146</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.1372414504513389</v>
+        <v>0.01375102413379979</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
@@ -3704,58 +3704,58 @@
         <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
         <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.02777179760986482</v>
+        <v>0.01002188754995696</v>
       </c>
       <c r="EQ6" t="n">
         <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.08432539398606216</v>
+        <v>-0.02222301620560347</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.05268916759156719</v>
+        <v>0.02593801603003642</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.006034778500994276</v>
+        <v>-0.01573291329435363</v>
       </c>
       <c r="EU6" t="n">
         <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.01688061356467228</v>
+        <v>0.1988269071318426</v>
       </c>
       <c r="EZ6" t="n">
         <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.02094187642274728</v>
+        <v>-0.02664955153714695</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.04992289103046275</v>
+        <v>-0.02267006589004343</v>
       </c>
       <c r="FC6" t="n">
-        <v>-0.1226431300979952</v>
+        <v>-0.09364513199318519</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>0</v>
@@ -3764,22 +3764,22 @@
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.08209028880258856</v>
+        <v>0.09873586394997787</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.06795702566002175</v>
+        <v>0.1413022637952358</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.04853720866109908</v>
+        <v>0.02563982407903588</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0.1283707880386293</v>
+        <v>0.005388985454496676</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
@@ -3791,19 +3791,19 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.08636451073218916</v>
+        <v>0.2833314232586847</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.01087369492814234</v>
+        <v>-0.2242104706882316</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1719228294189757</v>
+        <v>-0.04219355214840569</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0.03653346769023175</v>
+        <v>-0.0636749089859784</v>
       </c>
       <c r="FV6" t="n">
         <v>0</v>
@@ -3815,28 +3815,28 @@
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01673955448766197</v>
+        <v>0.1233447459284404</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0746382677999208</v>
+        <v>0.03566319604085755</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.106903269504374</v>
+        <v>-0.02312239607803645</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1097944988056291</v>
+        <v>0.5738901236051652</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02093762444485545</v>
+        <v>-0.0198635147852868</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06895013942223045</v>
+        <v>-0.2969531570775968</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08658429961889977</v>
+        <v>0.6543157764928708</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,70 +3883,70 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01332086292876557</v>
+        <v>-0.1806745552774211</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0598673684067033</v>
+        <v>-0.2577278036123049</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01522509612445713</v>
+        <v>0.1264560682107539</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01386746115135591</v>
+        <v>-0.1023021909366911</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.01325886517548903</v>
+        <v>-0.1155957767333536</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01698065468598606</v>
+        <v>0.1111364181807504</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01655606355426052</v>
+        <v>-0.2147284127330202</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0133554105440433</v>
+        <v>-0.04968275281705677</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.008732371348820753</v>
+        <v>0.2275334101513888</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.006106891713810333</v>
+        <v>0.0198217916420002</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04241573869008061</v>
+        <v>-0.2051141603484582</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,37 +3979,37 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.09986092833658361</v>
+        <v>1.036985737260395</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0006423682481677598</v>
+        <v>-0.3462905729077729</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.07540413021089218</v>
+        <v>-0.3165816035293733</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
         <v>-0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.06149378226141237</v>
+        <v>-0.03951600048404499</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,52 +4018,52 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.03419101506289174</v>
+        <v>-0.0653061363065558</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.04232287922094297</v>
+        <v>-0.2119197011060781</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0394051384013884</v>
+        <v>0.1731423856518274</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0143353797854996</v>
+        <v>0.1766979690213708</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.009285236152111256</v>
+        <v>0.06595136367971509</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05292083240395457</v>
+        <v>0.6389167563854679</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.009491437313510183</v>
+        <v>-0.1459944738319988</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.03712357641536285</v>
+        <v>-0.316590238913516</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4087,25 +4087,25 @@
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02828227658383355</v>
+        <v>-0.2991992888035941</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001731823683661432</v>
+        <v>0.04198389419049171</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.02278483859695817</v>
+        <v>0.1965153887510477</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,46 +4117,46 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.003002913171880829</v>
+        <v>-0.1867836150314625</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0005680093720727954</v>
+        <v>0.09419262938634355</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.004551690212151735</v>
+        <v>0.08409095173549785</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02242697222430126</v>
+        <v>-0.2866411215035243</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0009915750186827983</v>
+        <v>0.006046211183276333</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0270540504324927</v>
+        <v>0.1857905413296333</v>
       </c>
       <c r="DB7" t="n">
         <v>-0</v>
@@ -4171,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01093701439975773</v>
+        <v>-0.05035650550954296</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
@@ -4180,10 +4180,10 @@
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01098948196108129</v>
+        <v>-0.07668888697438306</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02791694298072734</v>
+        <v>0.02005470851622299</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,25 +4192,25 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.009399250736297391</v>
+        <v>-0.1151218984121012</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03042914271451878</v>
+        <v>-0.03285453989665943</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.003008071120035352</v>
+        <v>0.1177337365132406</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -4219,52 +4219,52 @@
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.02823312049691954</v>
+        <v>0.09691775507241548</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.009932367861490184</v>
+        <v>-0.01374706537047675</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0129485351744842</v>
+        <v>-0.07513368390695879</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.01742550158144157</v>
+        <v>-0.07201226575885314</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.007455588785387394</v>
+        <v>-0.1143533868528641</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.009248289153051408</v>
+        <v>0.1171481712675824</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4273,67 +4273,67 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.008693193702365825</v>
+        <v>-0.1858524843996021</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.008323031873037312</v>
+        <v>-0.05369222172987798</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01844899513821402</v>
+        <v>0.06842465651759483</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02339592474909429</v>
+        <v>-0.319032416550183</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.006728107130028157</v>
+        <v>-0.009186632421404557</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02818889319622977</v>
+        <v>0.1721556692225995</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.002578128928866239</v>
+        <v>-0.2804144741864795</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
@@ -4342,13 +4342,13 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02176887909126025</v>
+        <v>0.1446611357439511</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.03100994825920114</v>
+        <v>0.1505152423470378</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>0</v>
@@ -4357,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.008457826782753815</v>
+        <v>-0.1399741183222755</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,46 +4369,46 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.008945701380717817</v>
+        <v>0.05499036792942182</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0.001053673269432918</v>
+        <v>-0.008253151839928537</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01549910138829148</v>
+        <v>-0.1310614213381237</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.03576470712292852</v>
+        <v>0.004586251878915721</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3383443405243972</v>
+        <v>0.2843370589057069</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1505921141478772</v>
+        <v>-0.3037433377479419</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1155340187516716</v>
+        <v>0.02292064452449205</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,22 +4437,22 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3066728729800095</v>
+        <v>0.3256265048417927</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1173046619446357</v>
+        <v>-0.3034386245368852</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1302415933612011</v>
+        <v>0.02281081312396628</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4464,25 +4464,25 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08885819145904059</v>
+        <v>0.09103640400576028</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01838692296302995</v>
+        <v>-0.03228912367512462</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09415142377217792</v>
+        <v>-0.1866422349142943</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
@@ -4494,25 +4494,25 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1484901053989108</v>
+        <v>-0.00422844023494357</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01128518962678167</v>
+        <v>-0.1483513240323278</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01450723388530666</v>
+        <v>-0.1255771095651024</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,46 +4521,46 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01519318366141694</v>
+        <v>0.1597349615643745</v>
       </c>
       <c r="AM8" t="n">
         <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.06222693325943632</v>
+        <v>-0.07345567457092415</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.09324359993508043</v>
+        <v>0.04336106208369109</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4627236986800072</v>
+        <v>0.3950321130013201</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.04563353365331899</v>
+        <v>-0.1308450252973675</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.02023591216234698</v>
+        <v>-0.3035806616041938</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
@@ -4575,19 +4575,19 @@
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.06574489792983257</v>
+        <v>-0.08478301184500428</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.06780758097916388</v>
+        <v>-0.09251321622710429</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1025403724065054</v>
+        <v>-0.08146584995238874</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4605,16 +4605,16 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1232012818008523</v>
+        <v>0.002686346852633567</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.06552817040503883</v>
+        <v>0.09798772967894633</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1427478649561261</v>
+        <v>0.05866009341817481</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4632,49 +4632,49 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2763345974189239</v>
+        <v>0.2993027112797411</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.0307117811375514</v>
+        <v>-0.1512033766863409</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.07348777372219852</v>
+        <v>-0.09246201313402173</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.0906046108478252</v>
+        <v>-0.1548083280409569</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.02420751220147819</v>
+        <v>0.2121473112133031</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.01924390938378543</v>
+        <v>0.02720475435802436</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,52 +4686,52 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.05467895913892484</v>
+        <v>-0.02751911035553772</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.04856238429323619</v>
+        <v>0.3212740453858741</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.06199016587200314</v>
+        <v>0.0977196595563679</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.07745139893089138</v>
+        <v>-0.1340538852130376</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.04052651410928596</v>
+        <v>0.2220030840478792</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01185569518692343</v>
+        <v>0.03133568337508492</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,43 +4740,43 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.006748183583846532</v>
+        <v>0.01411315845718039</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1241619162828152</v>
+        <v>0.07984656543665862</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.008626499400173885</v>
+        <v>-0.03242976195692081</v>
       </c>
       <c r="DJ8" t="n">
         <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.08042244526726273</v>
+        <v>-0.1321444141161263</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.06703847540191057</v>
+        <v>0.16747467831105</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.0866073599479657</v>
+        <v>0.009870178487471735</v>
       </c>
       <c r="DS8" t="n">
         <v>-0</v>
@@ -4788,22 +4788,22 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.1153973068997162</v>
+        <v>-0.1107616024142232</v>
       </c>
       <c r="DY8" t="n">
         <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.02000673285354602</v>
+        <v>-0.1081050526182352</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.05628277720393418</v>
+        <v>-0.181634072840552</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,34 +4812,34 @@
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08699470789034841</v>
+        <v>-0.05621428837160812</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.07819054115150316</v>
+        <v>0.1361693488340511</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.1267367636414899</v>
+        <v>0.04817351713292038</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
@@ -4848,25 +4848,25 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.06488676253561834</v>
+        <v>-0.1139977207056184</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.03603250621704569</v>
+        <v>0.1365667816966553</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.07523080342250033</v>
+        <v>-0.0348687422854694</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
         <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
         <v>-0</v>
@@ -4875,16 +4875,16 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.07787644460483426</v>
+        <v>-0.1560744042019051</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.04600623410447618</v>
+        <v>0.2303933305063848</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.02808985923135017</v>
+        <v>0.008360287739959419</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
@@ -4893,52 +4893,52 @@
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.1134464479910015</v>
+        <v>-0.07241218954234717</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.05769299282695068</v>
+        <v>0.1014112830441577</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.06666336431957523</v>
+        <v>-0.2104300625416306</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01644431841158716</v>
+        <v>-0.03147046960172264</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>-0.02771690791957739</v>
+        <v>-0.0330553604331626</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.05309643694535925</v>
+        <v>0.09155102258660666</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
@@ -4953,16 +4953,16 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.05068129983594179</v>
+        <v>-0.105035495953188</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.01732920456701577</v>
+        <v>0.2150520149439369</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
@@ -4974,7 +4974,7 @@
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4982,34 +4982,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1274105081172724</v>
+        <v>0.119106604325581</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C9" t="n">
         <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09921172731217243</v>
+        <v>-0.2588922148307937</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1007893604557608</v>
+        <v>0.0691993719220144</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1302787597856077</v>
+        <v>0.09656251779274952</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -5018,25 +5018,25 @@
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03730910206144751</v>
+        <v>-0.3119810561330957</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04637360139756862</v>
+        <v>0.007778692754736394</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0247996049666238</v>
+        <v>-0.02559203413907064</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -5045,40 +5045,40 @@
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.05977521739887892</v>
+        <v>-0.06601532017365282</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04768670488093518</v>
+        <v>-0.055967498137423</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01852085957725397</v>
+        <v>0.02904573961386028</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01871132795936208</v>
+        <v>0.07299201197020339</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04216951160721504</v>
+        <v>0.2287623409238794</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5087,49 +5087,49 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.01347344147126953</v>
+        <v>0.02096817930759273</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.02018367403079253</v>
+        <v>-0.1876316459905757</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.06810611634096259</v>
+        <v>0.08382751856843366</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.09721437060501825</v>
+        <v>-0.0748253929121179</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.07575094777099746</v>
+        <v>-0.3961261376734601</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1587530121051314</v>
+        <v>-0.01212322578635378</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5144,7 +5144,7 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.1032721221389917</v>
+        <v>0.1613750692909476</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -5153,37 +5153,37 @@
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00888506747563037</v>
+        <v>0.2460760384616144</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0701353349805607</v>
+        <v>0.1546281874931391</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.05070689276073196</v>
+        <v>0.003813117454322032</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01641265501799957</v>
+        <v>0.01247594109246341</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1044615937544579</v>
+        <v>-0.1179006975502009</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
@@ -5192,40 +5192,40 @@
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.05050308571970946</v>
+        <v>-0.07989266932078012</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.01047944185756216</v>
+        <v>-0.3181404602414659</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.08298591883400638</v>
+        <v>-0.04579252694161192</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0.02788722047748494</v>
+        <v>-0.05706245585713163</v>
       </c>
       <c r="CE9" t="n">
         <v>0</v>
@@ -5234,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.01299306659463535</v>
+        <v>0.1261078068780819</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02769922872738519</v>
+        <v>-0.02139783643790253</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5249,37 +5249,37 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0.01936828525116053</v>
+        <v>0.009130837304713063</v>
       </c>
       <c r="CN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.05141081010287865</v>
+        <v>0.09554151196738975</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.04738197198998675</v>
+        <v>-0.04143216349017871</v>
       </c>
       <c r="CR9" t="n">
         <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0.01735213922875472</v>
+        <v>-0.04692898048878287</v>
       </c>
       <c r="CW9" t="n">
         <v>-0</v>
@@ -5288,10 +5288,10 @@
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0009267408852489555</v>
+        <v>0.1239634974524011</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01824293895837805</v>
+        <v>0.001096598117845166</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
@@ -5303,10 +5303,10 @@
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0.01330178546301631</v>
+        <v>-0.004169370328167164</v>
       </c>
       <c r="DF9" t="n">
         <v>-0</v>
@@ -5315,10 +5315,10 @@
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.07578372508899291</v>
+        <v>0.09588004113033222</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.03497142387663174</v>
+        <v>-0.02286482823406602</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
@@ -5330,10 +5330,10 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0.02322830444796386</v>
+        <v>-0.06991171994750708</v>
       </c>
       <c r="DO9" t="n">
         <v>-0</v>
@@ -5342,94 +5342,94 @@
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.04093374168895925</v>
+        <v>-0.01396544732022459</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.06672453508734329</v>
+        <v>0.02232396171996119</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0.03309153563836304</v>
+        <v>0.02605564510745069</v>
       </c>
       <c r="DX9" t="n">
         <v>-0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02603474053528315</v>
+        <v>0.02959944889519883</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02166553496663431</v>
+        <v>0.01765838542884414</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0.01617213704917918</v>
+        <v>-0.0789939374408319</v>
       </c>
       <c r="EG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.01836038796581111</v>
+        <v>0.09514996483524697</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.005579505243848418</v>
+        <v>0.04517218913551868</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0.0115898130128312</v>
+        <v>0.04089130157282954</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02220492024859829</v>
+        <v>0.1218243704214452</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01320430470978085</v>
+        <v>0.004314930673304873</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5441,19 +5441,19 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0.01802046526578398</v>
+        <v>-0.05273168257956194</v>
       </c>
       <c r="EY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.006617917298961641</v>
+        <v>0.1665887470274054</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02527579663017472</v>
+        <v>-0.01697562214757295</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
@@ -5465,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0.01475778016365977</v>
+        <v>0.05507885823117926</v>
       </c>
       <c r="FH9" t="n">
         <v>0</v>
@@ -5477,25 +5477,25 @@
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03061832585381027</v>
+        <v>0.108384088759285</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.1031396213704524</v>
+        <v>0.1444799158647086</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
         <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.005702482928402975</v>
+        <v>0.004035618915944237</v>
       </c>
       <c r="FQ9" t="n">
         <v>-0</v>
@@ -5504,40 +5504,40 @@
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.00538569467564255</v>
+        <v>0.2256435692504937</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.05251849715824964</v>
+        <v>0.07457444870741309</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.01583913216176002</v>
+        <v>0.03757132355243439</v>
       </c>
       <c r="FZ9" t="n">
         <v>0</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.01073087389460605</v>
+        <v>0.2357860266403936</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4279231561641801</v>
+        <v>0.2939188841566474</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1589869469382828</v>
+        <v>-0.2096050993674653</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03660992565160615</v>
+        <v>-0.03930977265735534</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2785515514023302</v>
+        <v>0.3102922503725093</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2117245904837028</v>
+        <v>-0.3084632299078136</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04132109131708741</v>
+        <v>-0.1270709448486535</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,76 +6746,76 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1049091428271091</v>
+        <v>0.05930623254144502</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01446832405444884</v>
+        <v>-0.08436321840105228</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09932689289879507</v>
+        <v>-0.1025596587602476</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04167995967873333</v>
+        <v>-0.04277491907528964</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.003692373712410086</v>
+        <v>-0.1632054664366957</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01337010712438213</v>
+        <v>-0.05913252539455142</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.00762882108756358</v>
+        <v>0.1157969822922773</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.06779017628110375</v>
+        <v>-0.1346757694247067</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.05742277807217042</v>
+        <v>0.03928841755514654</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6827,25 +6827,25 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.397193304397688</v>
+        <v>0.3071871092277548</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0205385954559788</v>
+        <v>-0.08496730604357783</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.09850396812810494</v>
+        <v>-0.2595197496006715</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05598126319333698</v>
+        <v>-0.01530499792942524</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1732124450079039</v>
+        <v>-0.0349223192578266</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1115140338875555</v>
+        <v>-0.01376103989122243</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1129161934917709</v>
+        <v>0.03609594191405226</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0466178222852079</v>
+        <v>0.0470771031862718</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1676713820224182</v>
+        <v>0.05139771796748598</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6902,79 +6902,79 @@
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1753781205997937</v>
+        <v>0.1942249485645745</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0178155021502691</v>
+        <v>-0.1579113756463411</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.06902469514657732</v>
+        <v>-0.08830883548545543</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.09154625162828724</v>
+        <v>-0.09800986833126611</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.001066055415028815</v>
+        <v>0.1253703938253296</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01504294802723569</v>
+        <v>0.02272813717702731</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.004418613229839737</v>
+        <v>-0.05342781881672947</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.08527387670721977</v>
+        <v>0.190009055064542</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.04920785941687961</v>
+        <v>0.05590423424008576</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.06416540034470133</v>
+        <v>-0.094023485328528</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03200906456610007</v>
+        <v>0.1364293359389348</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02319549863325032</v>
+        <v>0.03479683676322866</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7010,22 +7010,22 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03773425050010301</v>
+        <v>-0.04485478465090589</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04195238346698282</v>
+        <v>0.04040101360849777</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0747018921221935</v>
+        <v>-0.1185544738058205</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
@@ -7040,28 +7040,28 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06326358597731206</v>
+        <v>-0.08654476042757786</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0200184902200059</v>
+        <v>-0.04818819123102139</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.04040089330052701</v>
+        <v>0.00587079206010835</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,19 +7070,19 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.09758314151223167</v>
+        <v>-0.009914472694235815</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.01487454470074861</v>
+        <v>0.07956434805236391</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.03320343689284713</v>
+        <v>-0.04817624957897033</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08055139545154982</v>
+        <v>-0.05885840092462152</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01058959640830271</v>
+        <v>0.08612157692796762</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05741514176593135</v>
+        <v>0.05910897130768891</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
@@ -7115,31 +7115,31 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.01002762274187602</v>
+        <v>0.01287696631853613</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01341904244143164</v>
+        <v>0.08009224539214027</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02359625069369509</v>
+        <v>-0.03095458274618415</v>
       </c>
       <c r="ET12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,43 +7151,43 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06495968421901568</v>
+        <v>-0.1045490627774828</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.004441123833741585</v>
+        <v>0.1593787836742611</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.008467203535296319</v>
+        <v>0.009376349430355568</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.06264584782729475</v>
+        <v>0.124403335166709</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0.007555044852825596</v>
+        <v>0.105041947950116</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.04957299937506342</v>
+        <v>-0.01343857688004109</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,58 +7196,58 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.05378328263002635</v>
+        <v>0.04352996428824521</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01462006557752139</v>
+        <v>0.1614649947167993</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.05027579147419141</v>
+        <v>-0.02420534994942786</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.05742902244926062</v>
+        <v>-0.004125984124420166</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.1164042225091931</v>
+        <v>0.07403619774906947</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1418150113890258</v>
+        <v>0.2925473138956849</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,25 +7270,25 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.05212934777721806</v>
+        <v>-0.0006604997234588172</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0819161113298854</v>
+        <v>-0.141126492601485</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1192344406435505</v>
+        <v>0.3610406044044477</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,10 +7297,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04095649869977917</v>
+        <v>-0.08114790077522588</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.07582251746744344</v>
+        <v>-0.176018662847695</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7309,55 +7309,55 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01196876336721881</v>
+        <v>0.07961436300814562</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.006425497190614597</v>
+        <v>-0.1013749502649836</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01325100171852773</v>
+        <v>-0.007389068436715407</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.007264625703002387</v>
+        <v>-0.02864282605297995</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01855019913688282</v>
+        <v>-0.1835729358829446</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.007039344354325801</v>
+        <v>0.02762268508308182</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7369,34 +7369,34 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.007700401095348656</v>
+        <v>0.02740239893373322</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01288604712207817</v>
+        <v>-0.02884999842872245</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01279047310911076</v>
+        <v>0.0007866684706399864</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1046812517455351</v>
+        <v>0.2997618682648836</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,25 +7405,25 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01851524363540282</v>
+        <v>-0.2249486635873681</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.02489005858091989</v>
+        <v>-0.09076505601574504</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04377291656431273</v>
+        <v>-0.0005905598912101266</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,40 +7432,40 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.05406654001002854</v>
+        <v>-0.007191091550717709</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06265376379386371</v>
+        <v>-0.07313500164325319</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03975849246775683</v>
+        <v>0.03890167081070444</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02070067695915725</v>
+        <v>0.07023574808382337</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02039069701765887</v>
+        <v>-0.008477851550275669</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05136044246798737</v>
+        <v>0.1772179952082789</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.01168273282917597</v>
+        <v>-0.06124025182805251</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.008076658818782705</v>
+        <v>-0.1023478164554745</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,31 +7498,31 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.0257638648647999</v>
+        <v>-0.08726809214921016</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.003725703995507794</v>
+        <v>0.01600847386458473</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02222007007704993</v>
+        <v>0.04985145361821269</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.005663063808694237</v>
+        <v>-0.06356377826359472</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,43 +7540,43 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.002952023210437925</v>
+        <v>0.1079149426782336</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01617253273866866</v>
+        <v>0.05819651474099809</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.01936055904928424</v>
+        <v>-0.09079047412145513</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005348362761270307</v>
+        <v>0.008396395116826123</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02076653581258276</v>
+        <v>0.06846214879045207</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,19 +7585,19 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.01504997554724089</v>
+        <v>-0.01872280779506634</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02224854463538814</v>
+        <v>-0.1090698019751407</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.008558497652296524</v>
+        <v>0.05528884835021865</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
@@ -7606,82 +7606,82 @@
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.006262142993605922</v>
+        <v>-0.0286471441245943</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01764814668146044</v>
+        <v>-0.06339707095336301</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.00670030298383604</v>
+        <v>0.0360758215035295</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.0377514139143583</v>
+        <v>0.008239717554057689</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01755110630002733</v>
+        <v>-0.03476023524951392</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01059528448898435</v>
+        <v>0.01974661393767715</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.0285969772375216</v>
+        <v>-0.03227884906439711</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.004972922079231677</v>
+        <v>0.005679457537596598</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01951201754018511</v>
+        <v>0.004202522289365734</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.008653519282402045</v>
+        <v>-0.01311508678743446</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.005030109396400284</v>
+        <v>-0.007976787743528654</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.003537903002002638</v>
+        <v>0.08152561578247559</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,40 +7714,40 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0203501709139148</v>
+        <v>-0.1022007865763472</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.009312422251047356</v>
+        <v>-0.003330043336736445</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02627371647542371</v>
+        <v>0.04394784372701722</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01886967288879681</v>
+        <v>0.1610029764139557</v>
       </c>
       <c r="FI13" t="n">
         <v>0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.008232934798936815</v>
+        <v>-0.06563198580182787</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01643699731229806</v>
+        <v>0.1088475766100894</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,55 +7774,55 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.004206610798787966</v>
+        <v>0.05274451540377427</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0213006684902095</v>
+        <v>-0.08778362347351576</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01175768887509159</v>
+        <v>-0.02439524107513594</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0007349640975231169</v>
+        <v>-0.0309776968033058</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01020212477184129</v>
+        <v>0.06796946970744042</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,22 +7830,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4797805271022778</v>
+        <v>0.2482469937478071</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1852091826199542</v>
+        <v>-0.2166008339399337</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.06778738270545873</v>
+        <v>-0.05085274047477481</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
@@ -7857,16 +7857,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3224838527962762</v>
+        <v>0.2803215955290607</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2084002393092479</v>
+        <v>-0.2885214625250923</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.07830193356709939</v>
+        <v>-0.11538140043669</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7878,82 +7878,82 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1095507658166658</v>
+        <v>0.04573158121079301</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.01625776455020694</v>
+        <v>-0.0560132879357234</v>
       </c>
       <c r="W14" t="n">
-        <v>0.09311023085823629</v>
+        <v>-0.08790195094509848</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.04663299610649835</v>
+        <v>-0.06408823132118698</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.02606072695577923</v>
+        <v>-0.1133792804260067</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01321364913300729</v>
+        <v>-0.09544164024761505</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01801374058238342</v>
+        <v>0.1010524316628588</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06537906951489766</v>
+        <v>-0.101995314826544</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.05546673716189235</v>
+        <v>0.02371120336789841</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7965,25 +7965,25 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4293223750447213</v>
+        <v>0.2357881288261847</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02192520135728495</v>
+        <v>-0.09574427336185029</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.08956679125250813</v>
+        <v>-0.2390981338504744</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,25 +7992,25 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.04104273628811778</v>
+        <v>-0.02050839657776873</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1886207140115058</v>
+        <v>-0.04405695113151942</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1235864214280197</v>
+        <v>-0.009735949885674111</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,19 +8019,19 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1354131166472439</v>
+        <v>0.02697811842614867</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04544095500204342</v>
+        <v>0.07484545728073118</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.168352055449901</v>
+        <v>0.03635197015057019</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8040,49 +8040,49 @@
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1981215565126227</v>
+        <v>0.1550113295693692</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0138029648623435</v>
+        <v>-0.1389896247827818</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.06356184395951558</v>
+        <v>-0.0791716968460161</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.09379195038677345</v>
+        <v>-0.06395220839405821</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.008733418295613476</v>
+        <v>0.1206171132401933</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.009780134545292835</v>
+        <v>0.02358388127056904</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
@@ -8094,79 +8094,79 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.01272648288517118</v>
+        <v>-0.02559207788318069</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.07370164531575235</v>
+        <v>0.1657235022364415</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.07117424787767769</v>
+        <v>0.05948325521930394</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.06445219164809565</v>
+        <v>-0.06310937357646415</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.04077977417022122</v>
+        <v>0.1296054627363129</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01888159809260791</v>
+        <v>0.03071224329510754</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.04855299175287207</v>
+        <v>-0.05966246861666048</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04524326199585982</v>
+        <v>0.0220241541492367</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03123435189189423</v>
+        <v>-0.0337418575600645</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
@@ -8178,28 +8178,28 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.05679164838207558</v>
+        <v>-0.05232826888574188</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.009947891907231042</v>
+        <v>-0.03565241846216885</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.04746127824205065</v>
+        <v>0.001964866982827723</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,19 +8208,19 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.09817146471382365</v>
+        <v>0.02712254874026752</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.01052330853337616</v>
+        <v>0.06742818928516947</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.04955009235961691</v>
+        <v>-0.06094651220455547</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
@@ -8229,55 +8229,55 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.07830053880581145</v>
+        <v>-0.02811056859794352</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.01641333602679758</v>
+        <v>0.08772222291208855</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.06094548667999357</v>
+        <v>0.05175940344993012</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.002193325195148521</v>
+        <v>0.001359222487517479</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.007714535535193488</v>
+        <v>0.09325983661534359</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02997228094498673</v>
+        <v>-0.02506921614747175</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8289,22 +8289,22 @@
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.06453247484248251</v>
+        <v>-0.06779091173980491</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.006369784534682374</v>
+        <v>0.1514789047727031</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01325910691278161</v>
+        <v>0.006509082460071152</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8316,16 +8316,16 @@
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.05272781888620235</v>
+        <v>0.1255516832831165</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.007992074326585639</v>
+        <v>0.09804239067162829</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.05286821467286446</v>
+        <v>-0.04172101146961714</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8334,31 +8334,31 @@
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.043228319813299</v>
+        <v>0.02943614843536784</v>
       </c>
       <c r="FR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.01875773640838895</v>
+        <v>0.1500614262884907</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.0627179700324834</v>
+        <v>-0.04661075417658835</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
@@ -8367,25 +8367,25 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.05432453257358329</v>
+        <v>0.0100929547337886</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.110116341728181</v>
+        <v>0.04503587985808161</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3915996649459041</v>
+        <v>0.5102262115918758</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.09072086468595275</v>
+        <v>-0.006766245447887499</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2830721672286869</v>
+        <v>-0.4312697312378784</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8423,10 +8423,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3528816317886258</v>
+        <v>0.6630281724845497</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,16 +8435,16 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02483734293724342</v>
+        <v>-0.1431506960218502</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2585680256594056</v>
+        <v>-0.5177786006170643</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04064447962836121</v>
+        <v>0.1450465041964175</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,37 +8462,37 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.06130311767029282</v>
+        <v>-0.1187545358160736</v>
       </c>
       <c r="X15" t="n">
-        <v>7.049077711911252e-05</v>
+        <v>-0.09128684794451336</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.007899036486356779</v>
+        <v>-0.05786751549276268</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01368500499271937</v>
+        <v>-0.3001074265240586</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.01526120556275904</v>
+        <v>0.1562253051917037</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05775921626898211</v>
+        <v>0.1059113698012098</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.007485496319355423</v>
+        <v>-0.06697712057587975</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.07375764687103406</v>
+        <v>-0.08974019029748935</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,37 +8531,37 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2541213184003214</v>
+        <v>0.7733098583919249</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.05511290217264957</v>
+        <v>-0.3080101204003281</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.1452949888226114</v>
+        <v>-0.313019219063503</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.09172253198905023</v>
+        <v>-0.1175755493969561</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.06623352065693931</v>
+        <v>0.01204318853194076</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.09082033722312603</v>
+        <v>-0.039312686536397</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.08797427982319929</v>
+        <v>0.2029552122500499</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.02147090339613198</v>
+        <v>0.08658635718468999</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.03016701410453274</v>
+        <v>0.09707678152138427</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1439991914957534</v>
+        <v>0.4180411204425796</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,91 +8624,91 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.05020931203809727</v>
+        <v>-0.05458822018411747</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.07473641797218669</v>
+        <v>-0.2475579427132454</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.06473798834613056</v>
+        <v>-0.1606032994737381</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.006984513341847715</v>
+        <v>0.06025648882217664</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.06565947616930808</v>
+        <v>0.1276916571153235</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.005130152598004254</v>
+        <v>-0.2485877514007108</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.007291953387249714</v>
+        <v>0.1665187365470231</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.05247531358054943</v>
+        <v>0.02445912260253008</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.0558926493629594</v>
+        <v>-0.149259370104606</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.00379884336141284</v>
+        <v>0.03975168755226383</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.06898881540297949</v>
+        <v>0.1676740923917064</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8717,25 +8717,25 @@
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.06135915175399909</v>
+        <v>-0.1513624093886457</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08415556159940454</v>
+        <v>-0.1389562962581418</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.001882910752174652</v>
+        <v>0.03638157536833558</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,13 +8744,13 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02198602906121881</v>
+        <v>-0.05352875522714699</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
@@ -8759,160 +8759,160 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.02709105493686355</v>
+        <v>-0.001473616714997993</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01557499573893865</v>
+        <v>0.1489761392068431</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.04577995684550556</v>
+        <v>-0.04662496398318358</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02446729040975276</v>
+        <v>0.01743836428578572</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.03628187795870894</v>
+        <v>0.001949371353035528</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.0625351846790997</v>
+        <v>-0.04932475428619399</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
         <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01212071641359689</v>
+        <v>-0.005900836916335542</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.07125238700988845</v>
+        <v>0.02832001692035965</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.03925482114581458</v>
+        <v>-0.07466622391049144</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.02849246186004278</v>
+        <v>-0.07337426672667322</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.01543461448412817</v>
+        <v>-0.0374706779596977</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.05526825397540951</v>
+        <v>-0.1889299066450276</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.002552967613460943</v>
+        <v>0.01001908225771482</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.06744410034248326</v>
+        <v>0.1314301562561891</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.0150882359174045</v>
+        <v>0.1676108957568307</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>7.343728946793379e-05</v>
+        <v>-0.0784924012240636</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.04318257916738885</v>
+        <v>0.201792832338408</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.001735847605024572</v>
+        <v>0.1001835648649801</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,37 +8921,37 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.0445592454591066</v>
+        <v>-0.160806151166472</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.03884764812886873</v>
+        <v>-0.1482306912242548</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.02345443647110619</v>
+        <v>-0.0118814973036066</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.03031004375529048</v>
+        <v>0.195938826959501</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1459864676925804</v>
+        <v>0.3764316764668916</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,13 +8977,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04644232604711433</v>
+        <v>-0.1193365755701971</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0833227915646564</v>
+        <v>-0.1275861167472893</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1296064731831525</v>
+        <v>0.4660265104146602</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,67 +9004,67 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.03871110240628067</v>
+        <v>-0.2377030551541272</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.07995334038661481</v>
+        <v>-0.1774634238769862</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01521047641337729</v>
+        <v>0.1031123865755521</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.002830845724631298</v>
+        <v>-0.09214374448560091</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01529460053382572</v>
+        <v>-0.01659208342173435</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.006539045137681568</v>
+        <v>-0.04001125985904525</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01102629227921019</v>
+        <v>-0.2137609912400067</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.0001558048595554314</v>
+        <v>0.07524430605794083</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.01297094787824033</v>
+        <v>0.03098871310868441</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,25 +9085,25 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01178361479959298</v>
+        <v>-0.05298418402097968</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.009834037136126707</v>
+        <v>0.008961091288581738</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1005014334273454</v>
+        <v>0.4384166591175006</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,16 +9112,16 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.02505645121621535</v>
+        <v>-0.3010605702108101</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.03819922045526743</v>
+        <v>-0.1505278527313435</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.04070445156340922</v>
+        <v>-0.04220262973967508</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,40 +9139,40 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.04376064837965007</v>
+        <v>-0.02805089462870606</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.058763007623939</v>
+        <v>0.007077476069278439</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.04344680260462486</v>
+        <v>0.06924493817754034</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02865433732548747</v>
+        <v>0.08373332170460707</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01632526842713121</v>
+        <v>0.006705258651385004</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
@@ -9181,10 +9181,10 @@
         <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.04763348228080407</v>
+        <v>0.2423775006064492</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.005637753028236802</v>
+        <v>-0.09034156967456783</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.01131348686379291</v>
+        <v>-0.09849030671597903</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9208,28 +9208,28 @@
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.02232693483819628</v>
+        <v>-0.09530612684384594</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.003714059178834083</v>
+        <v>0.06389409685393108</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02225706331981295</v>
+        <v>0.04688620324193892</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.01594930237186459</v>
+        <v>-0.140894472294348</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,148 +9247,148 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.009295881439115073</v>
+        <v>0.1961103606830519</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.004410816959995088</v>
+        <v>0.04299939175098589</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.015590898225283</v>
+        <v>-0.09662289316780369</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.005758420897159645</v>
+        <v>0.05609538089898897</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.02166772380915599</v>
+        <v>0.06851804229554508</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03382510995906039</v>
+        <v>-0.03988650318085197</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02238230506447435</v>
+        <v>-0.1208265854193372</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.0004314575866276734</v>
+        <v>0.02135657672114676</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.01137881013406565</v>
+        <v>-0.004523598603709998</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.00824617705764065</v>
+        <v>-0.05585203043852375</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.01363273697851866</v>
+        <v>0.01609813161690306</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02474049572910414</v>
+        <v>-0.002472692482122132</v>
       </c>
       <c r="DY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01455239921255093</v>
+        <v>-0.003355394450046241</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.005100640975322824</v>
+        <v>-0.001509493460055001</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01920193022291034</v>
+        <v>-0.04321942579659008</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.003703542656038597</v>
+        <v>0.04747580571683346</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.01933329720553396</v>
+        <v>0.007534445615905796</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9400,79 +9400,79 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.004827386171694094</v>
+        <v>-0.02368662032265262</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.009454003317658223</v>
+        <v>0.004481991161459833</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.006505189430166875</v>
+        <v>0.07417922774115902</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01504456405110235</v>
+        <v>-0.1142908095851968</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.007587556470776972</v>
+        <v>0.04317840505877577</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02633074701446189</v>
+        <v>0.03885835781722507</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01373427251682238</v>
+        <v>0.1613828776524866</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.008850068795594896</v>
+        <v>-0.1031514966774304</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01677827084117568</v>
+        <v>0.09731195443751554</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,46 +9481,46 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.002956938044557995</v>
+        <v>0.07719016502198287</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.0208663456707841</v>
+        <v>-0.1514198436556562</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.006382432835950882</v>
+        <v>-0.06307412950728002</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.006444098791096322</v>
+        <v>-0.04929187675193637</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.006334992924899746</v>
+        <v>0.08975867399562142</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
